--- a/work/TEST.xlsx
+++ b/work/TEST.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="14">
   <si>
     <t>Име</t>
   </si>
@@ -27,19 +27,43 @@
     <t>Дата</t>
   </si>
   <si>
-    <t>Николина Дакова</t>
-  </si>
-  <si>
     <t>Участие в нещо</t>
   </si>
   <si>
-    <t>Ива Колчагова</t>
+    <t>Александър Костадинов</t>
+  </si>
+  <si>
+    <t>Борислав Илиев</t>
+  </si>
+  <si>
+    <t>Цветелина Василева</t>
+  </si>
+  <si>
+    <t>Даниел Тодоров</t>
+  </si>
+  <si>
+    <t>Златина Пенева</t>
+  </si>
+  <si>
+    <t>Калоян Маринов</t>
+  </si>
+  <si>
+    <t>Лилия Христова</t>
+  </si>
+  <si>
+    <t>Мартин Ангелов</t>
+  </si>
+  <si>
+    <t>Радостина Павлова</t>
+  </si>
+  <si>
+    <t>Симеон Захариев</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -74,7 +98,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Нормален" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -82,14 +106,17 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office тема">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Оffice">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -127,9 +154,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Оffice">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -164,7 +191,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -199,7 +226,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Оffice">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -373,15 +400,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.44140625" customWidth="1"/>
-    <col min="2" max="2" width="17.33203125" customWidth="1"/>
-    <col min="3" max="3" width="16.109375" customWidth="1"/>
+    <col min="1" max="1" width="32.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -392,25 +419,113 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" s="1">
         <v>46093</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" s="1">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="1">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="1">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="1">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" s="1">
         <v>46093</v>
       </c>
     </row>
@@ -422,7 +537,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -431,7 +546,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/work/TEST.xlsx
+++ b/work/TEST.xlsx
@@ -27,9 +27,6 @@
     <t>Дата</t>
   </si>
   <si>
-    <t>Участие в нещо</t>
-  </si>
-  <si>
     <t>Александър Костадинов</t>
   </si>
   <si>
@@ -58,6 +55,9 @@
   </si>
   <si>
     <t>Симеон Захариев</t>
+  </si>
+  <si>
+    <t>Тема/Курс</t>
   </si>
 </sst>
 </file>
@@ -421,10 +421,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C2" s="1">
         <v>46093</v>
@@ -432,10 +432,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C3" s="1">
         <v>46093</v>
@@ -443,10 +443,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C4" s="1">
         <v>46093</v>
@@ -454,10 +454,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1">
         <v>46093</v>
@@ -465,10 +465,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C6" s="1">
         <v>46093</v>
@@ -476,10 +476,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C7" s="1">
         <v>46093</v>
@@ -487,10 +487,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C8" s="1">
         <v>46093</v>
@@ -498,10 +498,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C9" s="1">
         <v>46093</v>
@@ -509,10 +509,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C10" s="1">
         <v>46093</v>
@@ -520,10 +520,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C11" s="1">
         <v>46093</v>
